--- a/reports/distilgpt2.xlsx
+++ b/reports/distilgpt2.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-09 14:27:06</t>
+          <t>2026-02-24 21:14:11</t>
         </is>
       </c>
     </row>
@@ -5976,9 +5976,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6133,9 +6133,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -18861,9 +18861,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B815" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B815" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -19149,9 +19149,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B843" s="12" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="B843" s="11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
